--- a/jogos_2025-06-13.xlsx
+++ b/jogos_2025-06-13.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="162">
   <si>
     <t>Date</t>
   </si>
@@ -235,12 +235,12 @@
     <t>Sweden Superettan</t>
   </si>
   <si>
+    <t>Republic of Ireland Premier Division</t>
+  </si>
+  <si>
     <t>Republic of Ireland First Division</t>
   </si>
   <si>
-    <t>Republic of Ireland Premier Division</t>
-  </si>
-  <si>
     <t>Uzbekistan Uzbekistan Super League</t>
   </si>
   <si>
@@ -250,12 +250,12 @@
     <t>Brazil Serie B</t>
   </si>
   <si>
+    <t>USA NWSL</t>
+  </si>
+  <si>
     <t>Chile Primera División</t>
   </si>
   <si>
-    <t>USA NWSL</t>
-  </si>
-  <si>
     <t>Argentina Prim B Nacional</t>
   </si>
   <si>
@@ -286,72 +286,72 @@
     <t>Örebro</t>
   </si>
   <si>
+    <t>Cork City</t>
+  </si>
+  <si>
+    <t>Dundalk</t>
+  </si>
+  <si>
     <t>Treaty United</t>
   </si>
   <si>
-    <t>Cork City</t>
-  </si>
-  <si>
     <t>Derry City</t>
   </si>
   <si>
+    <t>Athlone Town</t>
+  </si>
+  <si>
+    <t>St Patrick's Athl.</t>
+  </si>
+  <si>
+    <t>Finn Harps</t>
+  </si>
+  <si>
     <t>Shelbourne</t>
   </si>
   <si>
-    <t>Finn Harps</t>
-  </si>
-  <si>
-    <t>St Patrick's Athl.</t>
-  </si>
-  <si>
-    <t>Dundalk</t>
-  </si>
-  <si>
-    <t>Athlone Town</t>
+    <t>AGMK</t>
+  </si>
+  <si>
+    <t>Qizilqum</t>
+  </si>
+  <si>
+    <t>USM Alger</t>
+  </si>
+  <si>
+    <t>Vila Nova</t>
+  </si>
+  <si>
+    <t>ASO Chlef</t>
+  </si>
+  <si>
+    <t>ES Mostaganem</t>
+  </si>
+  <si>
+    <t>CR Belouizdad</t>
+  </si>
+  <si>
+    <t>NC Magra</t>
+  </si>
+  <si>
+    <t>JS Saoura</t>
+  </si>
+  <si>
+    <t>El Bayadh</t>
   </si>
   <si>
     <t>Bunyodkor</t>
   </si>
   <si>
-    <t>NC Magra</t>
-  </si>
-  <si>
-    <t>Qizilqum</t>
-  </si>
-  <si>
-    <t>AGMK</t>
-  </si>
-  <si>
     <t>US Biskra</t>
   </si>
   <si>
-    <t>El Bayadh</t>
-  </si>
-  <si>
-    <t>USM Alger</t>
-  </si>
-  <si>
-    <t>ASO Chlef</t>
-  </si>
-  <si>
-    <t>Vila Nova</t>
-  </si>
-  <si>
-    <t>ES Mostaganem</t>
-  </si>
-  <si>
-    <t>CR Belouizdad</t>
-  </si>
-  <si>
-    <t>JS Saoura</t>
+    <t>Houston Dash</t>
   </si>
   <si>
     <t>Deportes Limache</t>
   </si>
   <si>
-    <t>Houston Dash</t>
-  </si>
-  <si>
     <t>Paysandu</t>
   </si>
   <si>
@@ -388,72 +388,72 @@
     <t>Sandviken</t>
   </si>
   <si>
+    <t>Bohemians</t>
+  </si>
+  <si>
+    <t>UCD</t>
+  </si>
+  <si>
     <t>Bray Wanderers</t>
   </si>
   <si>
-    <t>Bohemians</t>
-  </si>
-  <si>
     <t>Galway United</t>
   </si>
   <si>
+    <t>Kerry</t>
+  </si>
+  <si>
+    <t>Drogheda United</t>
+  </si>
+  <si>
+    <t>Wexford</t>
+  </si>
+  <si>
     <t>Shamrock Rovers</t>
   </si>
   <si>
-    <t>Wexford</t>
-  </si>
-  <si>
-    <t>Drogheda United</t>
-  </si>
-  <si>
-    <t>UCD</t>
-  </si>
-  <si>
-    <t>Kerry</t>
+    <t>Shortan</t>
+  </si>
+  <si>
+    <t>Sogdiana</t>
+  </si>
+  <si>
+    <t>ES Sétif</t>
+  </si>
+  <si>
+    <t>América Mineiro</t>
+  </si>
+  <si>
+    <t>MC Alger</t>
+  </si>
+  <si>
+    <t>JS Kabylie</t>
+  </si>
+  <si>
+    <t>MC Oran</t>
+  </si>
+  <si>
+    <t>CS Constantine</t>
+  </si>
+  <si>
+    <t>Paradou AC</t>
+  </si>
+  <si>
+    <t>Oued Akbou</t>
   </si>
   <si>
     <t>Pakhtakor</t>
   </si>
   <si>
-    <t>CS Constantine</t>
-  </si>
-  <si>
-    <t>Sogdiana</t>
-  </si>
-  <si>
-    <t>Shortan</t>
-  </si>
-  <si>
     <t>USM Khenchela</t>
   </si>
   <si>
-    <t>Oued Akbou</t>
-  </si>
-  <si>
-    <t>ES Sétif</t>
-  </si>
-  <si>
-    <t>MC Alger</t>
-  </si>
-  <si>
-    <t>América Mineiro</t>
-  </si>
-  <si>
-    <t>JS Kabylie</t>
-  </si>
-  <si>
-    <t>MC Oran</t>
-  </si>
-  <si>
-    <t>Paradou AC</t>
+    <t>San Diego Wave</t>
   </si>
   <si>
     <t>Unión La Calera</t>
   </si>
   <si>
-    <t>San Diego Wave</t>
-  </si>
-  <si>
     <t>Botafogo SP</t>
   </si>
   <si>
@@ -472,10 +472,34 @@
     <t>SJ Earthquakes</t>
   </si>
   <si>
+    <t>complete</t>
+  </si>
+  <si>
     <t>incomplete</t>
   </si>
   <si>
     <t>[]</t>
+  </si>
+  <si>
+    <t>['9005']</t>
+  </si>
+  <si>
+    <t>['52']</t>
+  </si>
+  <si>
+    <t>['12', '32']</t>
+  </si>
+  <si>
+    <t>['36', '44']</t>
+  </si>
+  <si>
+    <t>['6', '32', '79']</t>
+  </si>
+  <si>
+    <t>['10', '55', '69']</t>
+  </si>
+  <si>
+    <t>['90+4']</t>
   </si>
 </sst>
 </file>
@@ -1035,13 +1059,13 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I2">
         <v>0</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K2" t="s">
         <v>152</v>
@@ -1095,10 +1119,10 @@
         <v>2.8</v>
       </c>
       <c r="AB2">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AC2">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="AD2">
         <v>4.2</v>
@@ -1119,10 +1143,10 @@
         <v>1.06</v>
       </c>
       <c r="AJ2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AK2" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="AL2">
         <v>1.75</v>
@@ -1134,7 +1158,7 @@
         <v>1.25</v>
       </c>
       <c r="AO2">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP2">
         <v>1.52</v>
@@ -1202,16 +1226,16 @@
         <v>119</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I3">
         <v>0</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" t="s">
         <v>152</v>
@@ -1265,10 +1289,10 @@
         <v>2.37</v>
       </c>
       <c r="AB3">
-        <v>2.4</v>
+        <v>2.43</v>
       </c>
       <c r="AC3">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AD3">
         <v>5</v>
@@ -1289,10 +1313,10 @@
         <v>1.05</v>
       </c>
       <c r="AJ3" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="AK3" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="AL3">
         <v>1.6</v>
@@ -1304,7 +1328,7 @@
         <v>1.3</v>
       </c>
       <c r="AO3">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP3">
         <v>1.47</v>
@@ -1372,7 +1396,7 @@
         <v>120</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4">
         <v>0</v>
@@ -1387,13 +1411,13 @@
         <v>152</v>
       </c>
       <c r="L4">
-        <v>1.8</v>
+        <v>1.63</v>
       </c>
       <c r="M4">
-        <v>3.95</v>
+        <v>3.92</v>
       </c>
       <c r="N4">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="O4">
         <v>1.44</v>
@@ -1459,10 +1483,10 @@
         <v>1.11</v>
       </c>
       <c r="AJ4" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="AK4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AL4">
         <v>1.14</v>
@@ -1474,7 +1498,7 @@
         <v>2.38</v>
       </c>
       <c r="AO4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP4">
         <v>1.19</v>
@@ -1542,13 +1566,13 @@
         <v>121</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H5">
         <v>0</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -1557,13 +1581,13 @@
         <v>152</v>
       </c>
       <c r="L5">
-        <v>1.76</v>
+        <v>1.86</v>
       </c>
       <c r="M5">
-        <v>3.9</v>
+        <v>3.69</v>
       </c>
       <c r="N5">
-        <v>4.1</v>
+        <v>3.45</v>
       </c>
       <c r="O5">
         <v>1.59</v>
@@ -1605,10 +1629,10 @@
         <v>3.88</v>
       </c>
       <c r="AB5">
-        <v>1.65</v>
+        <v>1.76</v>
       </c>
       <c r="AC5">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AD5">
         <v>2.7</v>
@@ -1629,10 +1653,10 @@
         <v>1.11</v>
       </c>
       <c r="AJ5" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="AK5" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AL5">
         <v>1.24</v>
@@ -1644,7 +1668,7 @@
         <v>1.94</v>
       </c>
       <c r="AO5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AP5">
         <v>1.28</v>
@@ -1712,13 +1736,13 @@
         <v>122</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -1727,13 +1751,13 @@
         <v>152</v>
       </c>
       <c r="L6">
-        <v>2.31</v>
+        <v>2.4</v>
       </c>
       <c r="M6">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="N6">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="O6">
         <v>1.8</v>
@@ -1745,76 +1769,76 @@
         <v>2.05</v>
       </c>
       <c r="R6">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="S6">
         <v>3.3</v>
       </c>
       <c r="T6">
-        <v>2.31</v>
+        <v>2.15</v>
       </c>
       <c r="U6">
         <v>1.6</v>
       </c>
       <c r="V6">
-        <v>5.15</v>
+        <v>5.3</v>
       </c>
       <c r="W6">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="X6">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y6">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="Z6">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AA6">
-        <v>4.6</v>
+        <v>4.75</v>
       </c>
       <c r="AB6">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AC6">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AD6">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="AE6">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AF6">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="AG6">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AH6">
-        <v>4.05</v>
+        <v>3.8</v>
       </c>
       <c r="AI6">
         <v>1.2</v>
       </c>
       <c r="AJ6" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="AK6" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="AL6">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="AM6">
         <v>1.22</v>
       </c>
       <c r="AN6">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AO6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP6">
         <v>0</v>
@@ -1894,7 +1918,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="L7">
         <v>2.38</v>
@@ -1969,10 +1993,10 @@
         <v>1.18</v>
       </c>
       <c r="AJ7" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AK7" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AL7">
         <v>1.45</v>
@@ -2064,127 +2088,127 @@
         <v>0</v>
       </c>
       <c r="K8" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="L8">
-        <v>2.2</v>
+        <v>3.85</v>
       </c>
       <c r="M8">
-        <v>3.3</v>
+        <v>3.64</v>
       </c>
       <c r="N8">
+        <v>1.87</v>
+      </c>
+      <c r="O8">
+        <v>2.88</v>
+      </c>
+      <c r="P8">
+        <v>8</v>
+      </c>
+      <c r="Q8">
+        <v>1.53</v>
+      </c>
+      <c r="R8">
+        <v>1.4</v>
+      </c>
+      <c r="S8">
         <v>2.75</v>
       </c>
-      <c r="O8">
+      <c r="T8">
+        <v>2.98</v>
+      </c>
+      <c r="U8">
+        <v>1.39</v>
+      </c>
+      <c r="V8">
+        <v>7</v>
+      </c>
+      <c r="W8">
+        <v>1.08</v>
+      </c>
+      <c r="X8">
+        <v>1.06</v>
+      </c>
+      <c r="Y8">
+        <v>9</v>
+      </c>
+      <c r="Z8">
+        <v>1.3</v>
+      </c>
+      <c r="AA8">
+        <v>3.25</v>
+      </c>
+      <c r="AB8">
+        <v>1.95</v>
+      </c>
+      <c r="AC8">
+        <v>1.88</v>
+      </c>
+      <c r="AD8">
+        <v>3.2</v>
+      </c>
+      <c r="AE8">
+        <v>1.3</v>
+      </c>
+      <c r="AF8">
         <v>1.8</v>
       </c>
-      <c r="P8">
-        <v>14.5</v>
-      </c>
-      <c r="Q8">
-        <v>2.03</v>
-      </c>
-      <c r="R8">
-        <v>1.35</v>
-      </c>
-      <c r="S8">
-        <v>3</v>
-      </c>
-      <c r="T8">
-        <v>2.57</v>
-      </c>
-      <c r="U8">
-        <v>1.45</v>
-      </c>
-      <c r="V8">
-        <v>5.8</v>
-      </c>
-      <c r="W8">
-        <v>1.1</v>
-      </c>
-      <c r="X8">
-        <v>1.04</v>
-      </c>
-      <c r="Y8">
-        <v>12</v>
-      </c>
-      <c r="Z8">
-        <v>1.22</v>
-      </c>
-      <c r="AA8">
-        <v>3.96</v>
-      </c>
-      <c r="AB8">
-        <v>1.72</v>
-      </c>
-      <c r="AC8">
-        <v>2</v>
-      </c>
-      <c r="AD8">
-        <v>2.8</v>
-      </c>
-      <c r="AE8">
-        <v>1.36</v>
-      </c>
-      <c r="AF8">
-        <v>1.62</v>
-      </c>
       <c r="AG8">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AH8">
-        <v>5</v>
+        <v>6.88</v>
       </c>
       <c r="AI8">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AJ8" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AK8" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AL8">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AM8">
         <v>1.25</v>
       </c>
       <c r="AN8">
-        <v>1.6</v>
+        <v>1.24</v>
       </c>
       <c r="AO8">
         <v>-1</v>
       </c>
       <c r="AP8">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AQ8">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AR8">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AS8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AT8">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AU8">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AV8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AW8">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AX8">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AY8">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AZ8">
         <v>0</v>
@@ -2193,10 +2217,10 @@
         <v>0</v>
       </c>
       <c r="BB8">
-        <v>1.8</v>
+        <v>2.88</v>
       </c>
       <c r="BC8">
-        <v>2.03</v>
+        <v>1.53</v>
       </c>
       <c r="BD8" s="3">
         <v>45821.65625</v>
@@ -2234,127 +2258,127 @@
         <v>0</v>
       </c>
       <c r="K9" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="L9">
+        <v>1.53</v>
+      </c>
+      <c r="M9">
         <v>3.75</v>
       </c>
-      <c r="M9">
-        <v>3.25</v>
-      </c>
       <c r="N9">
-        <v>1.8</v>
+        <v>5</v>
       </c>
       <c r="O9">
-        <v>2.88</v>
+        <v>1.4</v>
       </c>
       <c r="P9">
-        <v>8</v>
+        <v>9.1</v>
       </c>
       <c r="Q9">
-        <v>1.53</v>
+        <v>3.42</v>
       </c>
       <c r="R9">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="S9">
-        <v>2.62</v>
+        <v>2.95</v>
       </c>
       <c r="T9">
-        <v>3</v>
+        <v>2.65</v>
       </c>
       <c r="U9">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="V9">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="W9">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="X9">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y9">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="Z9">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="AA9">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="AB9">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="AC9">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="AD9">
-        <v>3.82</v>
+        <v>3.2</v>
       </c>
       <c r="AE9">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AF9">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AG9">
-        <v>1.8</v>
+        <v>1.68</v>
       </c>
       <c r="AH9">
-        <v>7.5</v>
+        <v>5.8</v>
       </c>
       <c r="AI9">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AJ9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AK9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AL9">
-        <v>1.87</v>
+        <v>1.2</v>
       </c>
       <c r="AM9">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AN9">
-        <v>1.22</v>
+        <v>2.35</v>
       </c>
       <c r="AO9">
         <v>-1</v>
       </c>
       <c r="AP9">
-        <v>1.17</v>
+        <v>1.38</v>
       </c>
       <c r="AQ9">
-        <v>1.34</v>
+        <v>1.7</v>
       </c>
       <c r="AR9">
-        <v>1.72</v>
+        <v>2.38</v>
       </c>
       <c r="AS9">
-        <v>1.98</v>
+        <v>2.7</v>
       </c>
       <c r="AT9">
-        <v>2.57</v>
+        <v>3.75</v>
       </c>
       <c r="AU9">
-        <v>3.7</v>
+        <v>2.83</v>
       </c>
       <c r="AV9">
-        <v>2.7</v>
+        <v>2.05</v>
       </c>
       <c r="AW9">
-        <v>2.08</v>
+        <v>1.66</v>
       </c>
       <c r="AX9">
-        <v>1.7</v>
+        <v>1.36</v>
       </c>
       <c r="AY9">
-        <v>1.42</v>
+        <v>1.19</v>
       </c>
       <c r="AZ9">
         <v>0</v>
@@ -2363,10 +2387,10 @@
         <v>0</v>
       </c>
       <c r="BB9">
-        <v>2.88</v>
+        <v>1.4</v>
       </c>
       <c r="BC9">
-        <v>1.53</v>
+        <v>3.42</v>
       </c>
       <c r="BD9" s="3">
         <v>45821.65625</v>
@@ -2404,127 +2428,127 @@
         <v>0</v>
       </c>
       <c r="K10" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="L10">
-        <v>1.86</v>
+        <v>2.38</v>
       </c>
       <c r="M10">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="N10">
-        <v>3.7</v>
+        <v>2.72</v>
       </c>
       <c r="O10">
-        <v>1.53</v>
+        <v>1.8</v>
       </c>
       <c r="P10">
-        <v>7</v>
+        <v>14.5</v>
       </c>
       <c r="Q10">
-        <v>3.1</v>
+        <v>2.03</v>
       </c>
       <c r="R10">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="S10">
-        <v>2.45</v>
+        <v>3</v>
       </c>
       <c r="T10">
-        <v>3.2</v>
+        <v>2.65</v>
       </c>
       <c r="U10">
-        <v>1.3</v>
+        <v>1.48</v>
       </c>
       <c r="V10">
-        <v>9</v>
+        <v>6.1</v>
       </c>
       <c r="W10">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X10">
         <v>1.04</v>
       </c>
       <c r="Y10">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Z10">
+        <v>1.22</v>
+      </c>
+      <c r="AA10">
+        <v>3.85</v>
+      </c>
+      <c r="AB10">
+        <v>1.76</v>
+      </c>
+      <c r="AC10">
+        <v>2.11</v>
+      </c>
+      <c r="AD10">
+        <v>2.8</v>
+      </c>
+      <c r="AE10">
         <v>1.4</v>
       </c>
-      <c r="AA10">
-        <v>2.75</v>
-      </c>
-      <c r="AB10">
-        <v>2.41</v>
-      </c>
-      <c r="AC10">
+      <c r="AF10">
         <v>1.55</v>
       </c>
-      <c r="AD10">
-        <v>4.75</v>
-      </c>
-      <c r="AE10">
-        <v>1.2</v>
-      </c>
-      <c r="AF10">
-        <v>2</v>
-      </c>
       <c r="AG10">
-        <v>1.63</v>
+        <v>2.23</v>
       </c>
       <c r="AH10">
-        <v>8.5</v>
+        <v>5.1</v>
       </c>
       <c r="AI10">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AJ10" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AK10" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AL10">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="AM10">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AN10">
-        <v>1.91</v>
+        <v>1.56</v>
       </c>
       <c r="AO10">
         <v>-1</v>
       </c>
       <c r="AP10">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AQ10">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="AR10">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AS10">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="AT10">
-        <v>3.05</v>
+        <v>3.14</v>
       </c>
       <c r="AU10">
-        <v>3.42</v>
+        <v>3.25</v>
       </c>
       <c r="AV10">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="AW10">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="AX10">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="AY10">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AZ10">
         <v>0</v>
@@ -2533,10 +2557,10 @@
         <v>0</v>
       </c>
       <c r="BB10">
-        <v>1.53</v>
+        <v>1.8</v>
       </c>
       <c r="BC10">
-        <v>3.1</v>
+        <v>2.03</v>
       </c>
       <c r="BD10" s="3">
         <v>45821.65625</v>
@@ -2550,7 +2574,7 @@
         <v>61</v>
       </c>
       <c r="C11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D11" t="s">
         <v>82</v>
@@ -2574,127 +2598,127 @@
         <v>0</v>
       </c>
       <c r="K11" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="L11">
-        <v>2.94</v>
+        <v>1.75</v>
       </c>
       <c r="M11">
-        <v>2.8</v>
+        <v>3.54</v>
       </c>
       <c r="N11">
-        <v>2.38</v>
+        <v>4.5</v>
       </c>
       <c r="O11">
-        <v>2.4</v>
+        <v>1.53</v>
       </c>
       <c r="P11">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="Q11">
-        <v>1.8</v>
+        <v>3.1</v>
       </c>
       <c r="R11">
-        <v>1.53</v>
+        <v>1.42</v>
       </c>
       <c r="S11">
-        <v>2.47</v>
+        <v>2.78</v>
       </c>
       <c r="T11">
-        <v>3.55</v>
+        <v>3.32</v>
       </c>
       <c r="U11">
-        <v>1.23</v>
+        <v>1.34</v>
       </c>
       <c r="V11">
-        <v>10</v>
+        <v>7.5</v>
       </c>
       <c r="W11">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="X11">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="Y11">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="Z11">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AA11">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="AB11">
-        <v>2.52</v>
+        <v>2.05</v>
       </c>
       <c r="AC11">
-        <v>1.51</v>
+        <v>1.74</v>
       </c>
       <c r="AD11">
-        <v>4.95</v>
+        <v>3.7</v>
       </c>
       <c r="AE11">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AF11">
+        <v>1.98</v>
+      </c>
+      <c r="AG11">
+        <v>1.83</v>
+      </c>
+      <c r="AH11">
+        <v>7</v>
+      </c>
+      <c r="AI11">
+        <v>1.06</v>
+      </c>
+      <c r="AJ11" t="s">
+        <v>154</v>
+      </c>
+      <c r="AK11" t="s">
+        <v>154</v>
+      </c>
+      <c r="AL11">
+        <v>1.31</v>
+      </c>
+      <c r="AM11">
+        <v>1.28</v>
+      </c>
+      <c r="AN11">
         <v>2.05</v>
-      </c>
-      <c r="AG11">
-        <v>1.73</v>
-      </c>
-      <c r="AH11">
-        <v>9</v>
-      </c>
-      <c r="AI11">
-        <v>1.03</v>
-      </c>
-      <c r="AJ11" t="s">
-        <v>153</v>
-      </c>
-      <c r="AK11" t="s">
-        <v>153</v>
-      </c>
-      <c r="AL11">
-        <v>1.36</v>
-      </c>
-      <c r="AM11">
-        <v>1.3</v>
-      </c>
-      <c r="AN11">
-        <v>1.25</v>
       </c>
       <c r="AO11">
         <v>-1</v>
       </c>
       <c r="AP11">
-        <v>1.36</v>
+        <v>1.24</v>
       </c>
       <c r="AQ11">
-        <v>1.61</v>
+        <v>1.44</v>
       </c>
       <c r="AR11">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="AS11">
-        <v>2.41</v>
+        <v>2.35</v>
       </c>
       <c r="AT11">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="AU11">
-        <v>2.8</v>
+        <v>3.6</v>
       </c>
       <c r="AV11">
-        <v>2.12</v>
+        <v>2.45</v>
       </c>
       <c r="AW11">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AX11">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="AY11">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AZ11">
         <v>0</v>
@@ -2703,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="BB11">
-        <v>2.4</v>
+        <v>1.53</v>
       </c>
       <c r="BC11">
-        <v>1.8</v>
+        <v>3.1</v>
       </c>
       <c r="BD11" s="3">
         <v>45821.65625</v>
@@ -2720,7 +2744,7 @@
         <v>61</v>
       </c>
       <c r="C12" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D12" t="s">
         <v>82</v>
@@ -2744,91 +2768,91 @@
         <v>0</v>
       </c>
       <c r="K12" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="L12">
+        <v>2.84</v>
+      </c>
+      <c r="M12">
+        <v>3.2</v>
+      </c>
+      <c r="N12">
+        <v>2.35</v>
+      </c>
+      <c r="O12">
+        <v>1.88</v>
+      </c>
+      <c r="P12">
+        <v>11.25</v>
+      </c>
+      <c r="Q12">
+        <v>2.02</v>
+      </c>
+      <c r="R12">
+        <v>1.38</v>
+      </c>
+      <c r="S12">
         <v>2.8</v>
       </c>
-      <c r="M12">
-        <v>3.3</v>
-      </c>
-      <c r="N12">
-        <v>2.17</v>
-      </c>
-      <c r="O12">
-        <v>2.07</v>
-      </c>
-      <c r="P12">
-        <v>12.5</v>
-      </c>
-      <c r="Q12">
-        <v>1.81</v>
-      </c>
-      <c r="R12">
-        <v>1.36</v>
-      </c>
-      <c r="S12">
-        <v>3</v>
-      </c>
       <c r="T12">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="U12">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="V12">
-        <v>7</v>
+        <v>6.75</v>
       </c>
       <c r="W12">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X12">
         <v>1.01</v>
       </c>
       <c r="Y12">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="Z12">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AA12">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="AB12">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AC12">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AD12">
-        <v>2.9</v>
+        <v>3.25</v>
       </c>
       <c r="AE12">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AF12">
-        <v>1.57</v>
+        <v>1.78</v>
       </c>
       <c r="AG12">
-        <v>2.1</v>
+        <v>1.96</v>
       </c>
       <c r="AH12">
-        <v>5.25</v>
+        <v>6</v>
       </c>
       <c r="AI12">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AJ12" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AK12" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AL12">
-        <v>1.24</v>
+        <v>1.55</v>
       </c>
       <c r="AM12">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AN12">
         <v>1.4</v>
@@ -2837,34 +2861,34 @@
         <v>-1</v>
       </c>
       <c r="AP12">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AQ12">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AR12">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AS12">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AT12">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AU12">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="AV12">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AW12">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AX12">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AY12">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AZ12">
         <v>0</v>
@@ -2873,10 +2897,10 @@
         <v>0</v>
       </c>
       <c r="BB12">
-        <v>2.07</v>
+        <v>1.88</v>
       </c>
       <c r="BC12">
-        <v>1.81</v>
+        <v>2.02</v>
       </c>
       <c r="BD12" s="3">
         <v>45821.65625</v>
@@ -2890,7 +2914,7 @@
         <v>61</v>
       </c>
       <c r="C13" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D13" t="s">
         <v>82</v>
@@ -2914,13 +2938,13 @@
         <v>0</v>
       </c>
       <c r="K13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="L13">
-        <v>1.74</v>
+        <v>1.65</v>
       </c>
       <c r="M13">
-        <v>3.68</v>
+        <v>3.72</v>
       </c>
       <c r="N13">
         <v>4.6</v>
@@ -2935,106 +2959,106 @@
         <v>3</v>
       </c>
       <c r="R13">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S13">
-        <v>2.62</v>
+        <v>2.81</v>
       </c>
       <c r="T13">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="U13">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="V13">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="W13">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X13">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y13">
-        <v>8.5</v>
+        <v>8.75</v>
       </c>
       <c r="Z13">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AA13">
+        <v>3.1</v>
+      </c>
+      <c r="AB13">
+        <v>1.93</v>
+      </c>
+      <c r="AC13">
+        <v>1.84</v>
+      </c>
+      <c r="AD13">
         <v>3.3</v>
       </c>
-      <c r="AB13">
-        <v>2.1</v>
-      </c>
-      <c r="AC13">
-        <v>1.75</v>
-      </c>
-      <c r="AD13">
-        <v>3.48</v>
-      </c>
       <c r="AE13">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AF13">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AG13">
-        <v>1.8</v>
+        <v>1.93</v>
       </c>
       <c r="AH13">
-        <v>6.55</v>
+        <v>7.27</v>
       </c>
       <c r="AI13">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AJ13" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AK13" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AL13">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AM13">
         <v>1.25</v>
       </c>
       <c r="AN13">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AO13">
         <v>-1</v>
       </c>
       <c r="AP13">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="AQ13">
-        <v>1.56</v>
+        <v>1.44</v>
       </c>
       <c r="AR13">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AS13">
-        <v>2.29</v>
+        <v>2.35</v>
       </c>
       <c r="AT13">
-        <v>3.08</v>
+        <v>3.2</v>
       </c>
       <c r="AU13">
-        <v>3.42</v>
+        <v>3.6</v>
       </c>
       <c r="AV13">
-        <v>2.23</v>
+        <v>2.45</v>
       </c>
       <c r="AW13">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="AX13">
         <v>1.49</v>
       </c>
       <c r="AY13">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="AZ13">
         <v>0</v>
@@ -3060,7 +3084,7 @@
         <v>61</v>
       </c>
       <c r="C14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D14" t="s">
         <v>82</v>
@@ -3084,127 +3108,127 @@
         <v>0</v>
       </c>
       <c r="K14" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="L14">
-        <v>1.48</v>
+        <v>2.86</v>
       </c>
       <c r="M14">
-        <v>4.1</v>
+        <v>3.35</v>
       </c>
       <c r="N14">
-        <v>5.6</v>
+        <v>1.95</v>
       </c>
       <c r="O14">
-        <v>1.4</v>
+        <v>2.07</v>
       </c>
       <c r="P14">
-        <v>9.1</v>
+        <v>12.5</v>
       </c>
       <c r="Q14">
-        <v>3.42</v>
+        <v>1.81</v>
       </c>
       <c r="R14">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="S14">
         <v>2.95</v>
       </c>
       <c r="T14">
-        <v>2.8</v>
+        <v>2.55</v>
       </c>
       <c r="U14">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="V14">
-        <v>6</v>
+        <v>6.25</v>
       </c>
       <c r="W14">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X14">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y14">
-        <v>9.1</v>
+        <v>8.6</v>
       </c>
       <c r="Z14">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AA14">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="AB14">
-        <v>1.86</v>
+        <v>1.7</v>
       </c>
       <c r="AC14">
-        <v>1.83</v>
+        <v>1.96</v>
       </c>
       <c r="AD14">
-        <v>3.2</v>
+        <v>2.78</v>
       </c>
       <c r="AE14">
+        <v>1.38</v>
+      </c>
+      <c r="AF14">
+        <v>1.62</v>
+      </c>
+      <c r="AG14">
+        <v>2.1</v>
+      </c>
+      <c r="AH14">
+        <v>5.1</v>
+      </c>
+      <c r="AI14">
+        <v>1.11</v>
+      </c>
+      <c r="AJ14" t="s">
+        <v>154</v>
+      </c>
+      <c r="AK14" t="s">
+        <v>154</v>
+      </c>
+      <c r="AL14">
+        <v>1.22</v>
+      </c>
+      <c r="AM14">
+        <v>1.27</v>
+      </c>
+      <c r="AN14">
         <v>1.3</v>
-      </c>
-      <c r="AF14">
-        <v>2</v>
-      </c>
-      <c r="AG14">
-        <v>1.77</v>
-      </c>
-      <c r="AH14">
-        <v>5.4</v>
-      </c>
-      <c r="AI14">
-        <v>1.07</v>
-      </c>
-      <c r="AJ14" t="s">
-        <v>153</v>
-      </c>
-      <c r="AK14" t="s">
-        <v>153</v>
-      </c>
-      <c r="AL14">
-        <v>1.25</v>
-      </c>
-      <c r="AM14">
-        <v>1.19</v>
-      </c>
-      <c r="AN14">
-        <v>2.48</v>
       </c>
       <c r="AO14">
         <v>-1</v>
       </c>
       <c r="AP14">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AQ14">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AR14">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AS14">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AT14">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AU14">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AV14">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AW14">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AX14">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AY14">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AZ14">
         <v>0</v>
@@ -3213,10 +3237,10 @@
         <v>0</v>
       </c>
       <c r="BB14">
-        <v>1.4</v>
+        <v>2.07</v>
       </c>
       <c r="BC14">
-        <v>3.42</v>
+        <v>1.81</v>
       </c>
       <c r="BD14" s="3">
         <v>45821.65625</v>
@@ -3254,127 +3278,127 @@
         <v>0</v>
       </c>
       <c r="K15" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="L15">
-        <v>2.37</v>
+        <v>3.3</v>
       </c>
       <c r="M15">
-        <v>3.2</v>
+        <v>3.24</v>
       </c>
       <c r="N15">
-        <v>2.7</v>
+        <v>2.1</v>
       </c>
       <c r="O15">
-        <v>1.88</v>
+        <v>2.4</v>
       </c>
       <c r="P15">
-        <v>11.25</v>
+        <v>6.5</v>
       </c>
       <c r="Q15">
-        <v>2.02</v>
+        <v>1.8</v>
       </c>
       <c r="R15">
-        <v>1.38</v>
+        <v>1.57</v>
       </c>
       <c r="S15">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="T15">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="U15">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="V15">
-        <v>6.75</v>
+        <v>9.75</v>
       </c>
       <c r="W15">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X15">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="Y15">
-        <v>8.5</v>
+        <v>6.5</v>
       </c>
       <c r="Z15">
-        <v>1.3</v>
+        <v>1.48</v>
       </c>
       <c r="AA15">
-        <v>3.22</v>
+        <v>2.66</v>
       </c>
       <c r="AB15">
-        <v>1.9</v>
+        <v>2.47</v>
       </c>
       <c r="AC15">
-        <v>1.8</v>
+        <v>1.56</v>
       </c>
       <c r="AD15">
-        <v>3.28</v>
+        <v>4.4</v>
       </c>
       <c r="AE15">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AF15">
-        <v>1.71</v>
+        <v>2.05</v>
       </c>
       <c r="AG15">
-        <v>2</v>
+        <v>1.66</v>
       </c>
       <c r="AH15">
-        <v>6.6</v>
+        <v>9.25</v>
       </c>
       <c r="AI15">
         <v>1.05</v>
       </c>
       <c r="AJ15" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AK15" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AL15">
-        <v>1.28</v>
+        <v>1.37</v>
       </c>
       <c r="AM15">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AN15">
-        <v>1.53</v>
+        <v>1.31</v>
       </c>
       <c r="AO15">
         <v>-1</v>
       </c>
       <c r="AP15">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AQ15">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AR15">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AS15">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AT15">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AU15">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AV15">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AW15">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AX15">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AY15">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AZ15">
         <v>0</v>
@@ -3383,10 +3407,10 @@
         <v>0</v>
       </c>
       <c r="BB15">
-        <v>1.88</v>
+        <v>2.4</v>
       </c>
       <c r="BC15">
-        <v>2.02</v>
+        <v>1.8</v>
       </c>
       <c r="BD15" s="3">
         <v>45821.65625</v>
@@ -3424,25 +3448,25 @@
         <v>0</v>
       </c>
       <c r="K16" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="L16">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="M16">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="P16">
         <v>0</v>
       </c>
       <c r="Q16">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="R16">
         <v>0</v>
@@ -3475,10 +3499,10 @@
         <v>0</v>
       </c>
       <c r="AB16">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC16">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD16">
         <v>0</v>
@@ -3499,10 +3523,10 @@
         <v>0</v>
       </c>
       <c r="AJ16" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AK16" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3553,10 +3577,10 @@
         <v>0</v>
       </c>
       <c r="BB16">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC16">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="BD16" s="3">
         <v>45821.79166666666</v>
@@ -3570,10 +3594,10 @@
         <v>62</v>
       </c>
       <c r="C17" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D17" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E17" t="s">
         <v>99</v>
@@ -3594,25 +3618,25 @@
         <v>0</v>
       </c>
       <c r="K17" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="L17">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="M17">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P17">
         <v>0</v>
       </c>
       <c r="Q17">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="R17">
         <v>0</v>
@@ -3645,10 +3669,10 @@
         <v>0</v>
       </c>
       <c r="AB17">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AC17">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AD17">
         <v>0</v>
@@ -3669,10 +3693,10 @@
         <v>0</v>
       </c>
       <c r="AJ17" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AK17" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3723,10 +3747,10 @@
         <v>0</v>
       </c>
       <c r="BB17">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="BC17">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="BD17" s="3">
         <v>45821.79166666666</v>
@@ -3740,10 +3764,10 @@
         <v>62</v>
       </c>
       <c r="C18" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D18" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E18" t="s">
         <v>100</v>
@@ -3764,7 +3788,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="L18">
         <v>0</v>
@@ -3839,10 +3863,10 @@
         <v>0</v>
       </c>
       <c r="AJ18" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AK18" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3910,7 +3934,7 @@
         <v>62</v>
       </c>
       <c r="C19" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D19" t="s">
         <v>82</v>
@@ -3934,127 +3958,127 @@
         <v>0</v>
       </c>
       <c r="K19" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="L19">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M19">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="T19">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U19">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V19">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="W19">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X19">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Y19">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Z19">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AA19">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB19">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AC19">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AD19">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AE19">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF19">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG19">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH19">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AI19">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AJ19" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AK19" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AL19">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AM19">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AN19">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AO19">
         <v>-1</v>
       </c>
       <c r="AP19">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AQ19">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AR19">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AS19">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AT19">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AU19">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AV19">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AW19">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AX19">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AY19">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AZ19">
         <v>0</v>
@@ -4063,10 +4087,10 @@
         <v>0</v>
       </c>
       <c r="BB19">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="BC19">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="BD19" s="3">
         <v>45821.79166666666</v>
@@ -4104,7 +4128,7 @@
         <v>0</v>
       </c>
       <c r="K20" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="L20">
         <v>0</v>
@@ -4179,10 +4203,10 @@
         <v>0</v>
       </c>
       <c r="AJ20" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AK20" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -4274,7 +4298,7 @@
         <v>0</v>
       </c>
       <c r="K21" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="L21">
         <v>0</v>
@@ -4349,10 +4373,10 @@
         <v>0</v>
       </c>
       <c r="AJ21" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AK21" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -4444,7 +4468,7 @@
         <v>0</v>
       </c>
       <c r="K22" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="L22">
         <v>0</v>
@@ -4519,10 +4543,10 @@
         <v>0</v>
       </c>
       <c r="AJ22" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AK22" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4614,7 +4638,7 @@
         <v>0</v>
       </c>
       <c r="K23" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="L23">
         <v>0</v>
@@ -4689,10 +4713,10 @@
         <v>0</v>
       </c>
       <c r="AJ23" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AK23" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4760,10 +4784,10 @@
         <v>62</v>
       </c>
       <c r="C24" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D24" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E24" t="s">
         <v>106</v>
@@ -4784,127 +4808,127 @@
         <v>0</v>
       </c>
       <c r="K24" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="L24">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="M24">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N24">
-        <v>4.27</v>
+        <v>0</v>
       </c>
       <c r="O24">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="P24">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="Q24">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="R24">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S24">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="T24">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="U24">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="V24">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="W24">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X24">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="Y24">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="Z24">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AA24">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB24">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AC24">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AD24">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AE24">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AF24">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AG24">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AH24">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AI24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ24" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AK24" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AL24">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AM24">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AN24">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AO24">
         <v>-1</v>
       </c>
       <c r="AP24">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AQ24">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AR24">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AS24">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AT24">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AU24">
-        <v>5.45</v>
+        <v>0</v>
       </c>
       <c r="AV24">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AW24">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="AX24">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AY24">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AZ24">
         <v>0</v>
@@ -4913,10 +4937,10 @@
         <v>0</v>
       </c>
       <c r="BB24">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="BC24">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="BD24" s="3">
         <v>45821.79166666666</v>
@@ -4954,7 +4978,7 @@
         <v>0</v>
       </c>
       <c r="K25" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="L25">
         <v>0</v>
@@ -5029,10 +5053,10 @@
         <v>0</v>
       </c>
       <c r="AJ25" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AK25" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -5100,10 +5124,10 @@
         <v>62</v>
       </c>
       <c r="C26" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D26" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E26" t="s">
         <v>108</v>
@@ -5124,25 +5148,25 @@
         <v>0</v>
       </c>
       <c r="K26" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="L26">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="M26">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="N26">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O26">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="P26">
         <v>0</v>
       </c>
       <c r="Q26">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="R26">
         <v>0</v>
@@ -5175,10 +5199,10 @@
         <v>0</v>
       </c>
       <c r="AB26">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC26">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD26">
         <v>0</v>
@@ -5199,10 +5223,10 @@
         <v>0</v>
       </c>
       <c r="AJ26" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AK26" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -5253,10 +5277,10 @@
         <v>0</v>
       </c>
       <c r="BB26">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="BC26">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="BD26" s="3">
         <v>45821.79166666666</v>
@@ -5294,16 +5318,16 @@
         <v>0</v>
       </c>
       <c r="K27" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="L27">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="M27">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N27">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O27">
         <v>0</v>
@@ -5369,10 +5393,10 @@
         <v>0</v>
       </c>
       <c r="AJ27" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AK27" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -5464,127 +5488,127 @@
         <v>0</v>
       </c>
       <c r="K28" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="L28">
-        <v>2.12</v>
+        <v>3.46</v>
       </c>
       <c r="M28">
-        <v>3.43</v>
+        <v>3.45</v>
       </c>
       <c r="N28">
-        <v>3.36</v>
+        <v>1.92</v>
       </c>
       <c r="O28">
+        <v>2.88</v>
+      </c>
+      <c r="P28">
+        <v>0</v>
+      </c>
+      <c r="Q28">
+        <v>1.57</v>
+      </c>
+      <c r="R28">
+        <v>1.33</v>
+      </c>
+      <c r="S28">
+        <v>3.15</v>
+      </c>
+      <c r="T28">
+        <v>2.56</v>
+      </c>
+      <c r="U28">
+        <v>1.44</v>
+      </c>
+      <c r="V28">
+        <v>6</v>
+      </c>
+      <c r="W28">
+        <v>1.1</v>
+      </c>
+      <c r="X28">
+        <v>1.04</v>
+      </c>
+      <c r="Y28">
+        <v>12</v>
+      </c>
+      <c r="Z28">
+        <v>1.2</v>
+      </c>
+      <c r="AA28">
+        <v>4</v>
+      </c>
+      <c r="AB28">
+        <v>1.7</v>
+      </c>
+      <c r="AC28">
+        <v>2.05</v>
+      </c>
+      <c r="AD28">
+        <v>2.7</v>
+      </c>
+      <c r="AE28">
+        <v>1.4</v>
+      </c>
+      <c r="AF28">
         <v>1.67</v>
       </c>
-      <c r="P28">
-        <v>7.8</v>
-      </c>
-      <c r="Q28">
-        <v>2.5</v>
-      </c>
-      <c r="R28">
-        <v>1.44</v>
-      </c>
-      <c r="S28">
-        <v>2.63</v>
-      </c>
-      <c r="T28">
-        <v>3.25</v>
-      </c>
-      <c r="U28">
-        <v>1.33</v>
-      </c>
-      <c r="V28">
-        <v>10</v>
-      </c>
-      <c r="W28">
-        <v>1.06</v>
-      </c>
-      <c r="X28">
-        <v>1.02</v>
-      </c>
-      <c r="Y28">
-        <v>7.8</v>
-      </c>
-      <c r="Z28">
-        <v>1.41</v>
-      </c>
-      <c r="AA28">
-        <v>2.83</v>
-      </c>
-      <c r="AB28">
-        <v>2.25</v>
-      </c>
-      <c r="AC28">
-        <v>1.62</v>
-      </c>
-      <c r="AD28">
-        <v>4.05</v>
-      </c>
-      <c r="AE28">
-        <v>1.17</v>
-      </c>
-      <c r="AF28">
-        <v>1.91</v>
-      </c>
       <c r="AG28">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="AH28">
-        <v>8.199999999999999</v>
+        <v>5</v>
       </c>
       <c r="AI28">
-        <v>1.02</v>
+        <v>1.15</v>
       </c>
       <c r="AJ28" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AK28" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AL28">
+        <v>1.25</v>
+      </c>
+      <c r="AM28">
+        <v>0</v>
+      </c>
+      <c r="AN28">
         <v>1.3</v>
-      </c>
-      <c r="AM28">
-        <v>1.35</v>
-      </c>
-      <c r="AN28">
-        <v>1.7</v>
       </c>
       <c r="AO28">
         <v>-1</v>
       </c>
       <c r="AP28">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AQ28">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AR28">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AS28">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AT28">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AU28">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AV28">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AW28">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AX28">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AY28">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AZ28">
         <v>0</v>
@@ -5593,10 +5617,10 @@
         <v>0</v>
       </c>
       <c r="BB28">
-        <v>1.67</v>
+        <v>2.88</v>
       </c>
       <c r="BC28">
-        <v>2.5</v>
+        <v>1.57</v>
       </c>
       <c r="BD28" s="3">
         <v>45821.875</v>
@@ -5634,127 +5658,127 @@
         <v>0</v>
       </c>
       <c r="K29" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="L29">
-        <v>3.45</v>
+        <v>2.12</v>
       </c>
       <c r="M29">
-        <v>3.26</v>
+        <v>3.43</v>
       </c>
       <c r="N29">
-        <v>2.03</v>
+        <v>3.36</v>
       </c>
       <c r="O29">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="P29">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="Q29">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R29">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="S29">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="T29">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="U29">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="V29">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W29">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X29">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y29">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="Z29">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="AA29">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="AB29">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AC29">
         <v>1.62</v>
       </c>
       <c r="AD29">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="AE29">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AF29">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AG29">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AH29">
-        <v>7.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AI29">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AJ29" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AK29" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AL29">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AM29">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AN29">
-        <v>1.33</v>
+        <v>1.7</v>
       </c>
       <c r="AO29">
         <v>-1</v>
       </c>
       <c r="AP29">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AQ29">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AR29">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AS29">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AT29">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AU29">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AV29">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AW29">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AX29">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AY29">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AZ29">
         <v>0</v>
@@ -5763,10 +5787,10 @@
         <v>0</v>
       </c>
       <c r="BB29">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="BC29">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="BD29" s="3">
         <v>45821.875</v>
@@ -5804,16 +5828,16 @@
         <v>0</v>
       </c>
       <c r="K30" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="L30">
-        <v>1.86</v>
+        <v>1.98</v>
       </c>
       <c r="M30">
-        <v>3.42</v>
+        <v>3</v>
       </c>
       <c r="N30">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="O30">
         <v>1.65</v>
@@ -5825,106 +5849,106 @@
         <v>2.75</v>
       </c>
       <c r="R30">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="S30">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="T30">
-        <v>3.2</v>
+        <v>3.56</v>
       </c>
       <c r="U30">
         <v>1.27</v>
       </c>
       <c r="V30">
-        <v>6.8</v>
+        <v>9.5</v>
       </c>
       <c r="W30">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X30">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="Y30">
-        <v>8.300000000000001</v>
+        <v>6.5</v>
       </c>
       <c r="Z30">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="AA30">
-        <v>2.88</v>
+        <v>2.53</v>
       </c>
       <c r="AB30">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="AC30">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AD30">
-        <v>4.33</v>
+        <v>5</v>
       </c>
       <c r="AE30">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AF30">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AG30">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AH30">
         <v>8.300000000000001</v>
       </c>
       <c r="AI30">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AJ30" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AK30" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AL30">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AM30">
         <v>1.32</v>
       </c>
       <c r="AN30">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="AO30">
         <v>-1</v>
       </c>
       <c r="AP30">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AQ30">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="AR30">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AS30">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AT30">
-        <v>2.52</v>
+        <v>2.46</v>
       </c>
       <c r="AU30">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AV30">
-        <v>2.78</v>
+        <v>2.9</v>
       </c>
       <c r="AW30">
-        <v>2.17</v>
+        <v>2.22</v>
       </c>
       <c r="AX30">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="AY30">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="AZ30">
         <v>0</v>
@@ -5974,127 +5998,127 @@
         <v>0</v>
       </c>
       <c r="K31" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="L31">
-        <v>2.61</v>
+        <v>2.4</v>
       </c>
       <c r="M31">
-        <v>2.51</v>
+        <v>2.55</v>
       </c>
       <c r="N31">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="O31">
         <v>1.95</v>
       </c>
       <c r="P31">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="Q31">
         <v>2.6</v>
       </c>
       <c r="R31">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="S31">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="T31">
         <v>4.5</v>
       </c>
       <c r="U31">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="V31">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="W31">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X31">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Y31">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Z31">
-        <v>1.76</v>
+        <v>1.85</v>
       </c>
       <c r="AA31">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="AB31">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="AC31">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AD31">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AE31">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF31">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="AG31">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AH31">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AI31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AJ31" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AK31" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AL31">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AM31">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AN31">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AO31">
         <v>-1</v>
       </c>
       <c r="AP31">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AQ31">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AR31">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="AS31">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AT31">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AU31">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AV31">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AW31">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AX31">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AY31">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AZ31">
         <v>0</v>
@@ -6120,7 +6144,7 @@
         <v>66</v>
       </c>
       <c r="C32" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D32" t="s">
         <v>82</v>
@@ -6144,16 +6168,16 @@
         <v>0</v>
       </c>
       <c r="K32" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="L32">
-        <v>4.55</v>
+        <v>3.75</v>
       </c>
       <c r="M32">
-        <v>3.44</v>
+        <v>3.5</v>
       </c>
       <c r="N32">
-        <v>1.67</v>
+        <v>1.78</v>
       </c>
       <c r="O32">
         <v>3.25</v>
@@ -6165,64 +6189,64 @@
         <v>1.5</v>
       </c>
       <c r="R32">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="S32">
-        <v>2.61</v>
+        <v>3</v>
       </c>
       <c r="T32">
-        <v>3</v>
+        <v>2.55</v>
       </c>
       <c r="U32">
-        <v>1.33</v>
+        <v>1.48</v>
       </c>
       <c r="V32">
-        <v>7.5</v>
+        <v>5.75</v>
       </c>
       <c r="W32">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X32">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y32">
-        <v>6.4</v>
+        <v>11</v>
       </c>
       <c r="Z32">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AA32">
-        <v>2.95</v>
+        <v>3.75</v>
       </c>
       <c r="AB32">
-        <v>2.15</v>
+        <v>1.75</v>
       </c>
       <c r="AC32">
-        <v>1.56</v>
+        <v>1.95</v>
       </c>
       <c r="AD32">
-        <v>3.58</v>
+        <v>2.88</v>
       </c>
       <c r="AE32">
-        <v>1.19</v>
+        <v>1.37</v>
       </c>
       <c r="AF32">
-        <v>2.14</v>
+        <v>1.73</v>
       </c>
       <c r="AG32">
-        <v>1.73</v>
+        <v>2.03</v>
       </c>
       <c r="AH32">
-        <v>7</v>
+        <v>4.6</v>
       </c>
       <c r="AI32">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="AJ32" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AK32" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AL32">
         <v>1.29</v>
@@ -6231,7 +6255,7 @@
         <v>0</v>
       </c>
       <c r="AN32">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AO32">
         <v>-1</v>
@@ -6240,7 +6264,7 @@
         <v>0</v>
       </c>
       <c r="AQ32">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AR32">
         <v>0</v>
@@ -6255,7 +6279,7 @@
         <v>0</v>
       </c>
       <c r="AV32">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AW32">
         <v>0</v>
@@ -6290,7 +6314,7 @@
         <v>67</v>
       </c>
       <c r="C33" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D33" t="s">
         <v>82</v>
@@ -6314,16 +6338,16 @@
         <v>0</v>
       </c>
       <c r="K33" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="L33">
-        <v>4.76</v>
+        <v>3.5</v>
       </c>
       <c r="M33">
-        <v>3.68</v>
+        <v>3.4</v>
       </c>
       <c r="N33">
-        <v>1.62</v>
+        <v>1.83</v>
       </c>
       <c r="O33">
         <v>0</v>
@@ -6338,13 +6362,13 @@
         <v>1.33</v>
       </c>
       <c r="S33">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="T33">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="U33">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="V33">
         <v>6</v>
@@ -6356,52 +6380,52 @@
         <v>1.02</v>
       </c>
       <c r="Y33">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Z33">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AA33">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="AB33">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AC33">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AD33">
-        <v>2.97</v>
+        <v>2.9</v>
       </c>
       <c r="AE33">
-        <v>1.24</v>
+        <v>1.36</v>
       </c>
       <c r="AF33">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AG33">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="AH33">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="AI33">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="AJ33" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AK33" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AL33">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="AM33">
         <v>0</v>
       </c>
       <c r="AN33">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AO33">
         <v>-1</v>
@@ -6484,7 +6508,7 @@
         <v>0</v>
       </c>
       <c r="K34" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="L34">
         <v>0</v>
@@ -6559,10 +6583,10 @@
         <v>0</v>
       </c>
       <c r="AJ34" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AK34" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6654,7 +6678,7 @@
         <v>0</v>
       </c>
       <c r="K35" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="L35">
         <v>1.77</v>
@@ -6705,16 +6729,16 @@
         <v>5.25</v>
       </c>
       <c r="AB35">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AC35">
-        <v>2.6</v>
+        <v>2.78</v>
       </c>
       <c r="AD35">
-        <v>2.15</v>
+        <v>1.94</v>
       </c>
       <c r="AE35">
-        <v>1.61</v>
+        <v>1.76</v>
       </c>
       <c r="AF35">
         <v>1.44</v>
@@ -6729,10 +6753,10 @@
         <v>1.28</v>
       </c>
       <c r="AJ35" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AK35" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AL35">
         <v>1.25</v>

--- a/jogos_2025-06-13.xlsx
+++ b/jogos_2025-06-13.xlsx
@@ -643,16 +643,16 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
         <v>3</v>
@@ -661,7 +661,7 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -669,83 +669,83 @@
         </is>
       </c>
       <c r="L2" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="M2" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="N2" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="O2" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="P2" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S2" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T2" t="n">
         <v>3.25</v>
       </c>
-      <c r="M2" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="N2" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="O2" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>3</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="S2" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="T2" t="n">
-        <v>3.5</v>
-      </c>
       <c r="U2" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="V2" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="W2" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="X2" t="n">
-        <v>2.37</v>
+        <v>2.8</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.43</v>
+        <v>2.05</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.49</v>
+        <v>1.68</v>
       </c>
       <c r="AA2" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>['9005']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>['10', '55', '69']</t>
+          <t>['6', '32', '79']</t>
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AI2" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AK2" s="3" t="n">
         <v>45821.3125</v>
@@ -772,16 +772,16 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
         <v>3</v>
@@ -790,7 +790,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -798,83 +798,83 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3.62</v>
+        <v>3.25</v>
       </c>
       <c r="M3" t="n">
-        <v>3.11</v>
+        <v>2.9</v>
       </c>
       <c r="N3" t="n">
-        <v>1.92</v>
+        <v>2.14</v>
       </c>
       <c r="O3" t="n">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="P3" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.63</v>
+        <v>3</v>
       </c>
       <c r="R3" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="S3" t="n">
-        <v>2.63</v>
+        <v>2.38</v>
       </c>
       <c r="T3" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="U3" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="V3" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="W3" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="X3" t="n">
-        <v>2.8</v>
+        <v>2.37</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.05</v>
+        <v>2.43</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.68</v>
+        <v>1.49</v>
       </c>
       <c r="AA3" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['9005']</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>['6', '32', '79']</t>
+          <t>['10', '55', '69']</t>
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AI3" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="AK3" s="3" t="n">
         <v>45821.3125</v>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,109 +1159,109 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>4</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
         <v>1</v>
       </c>
-      <c r="H6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
       <c r="K6" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.57</v>
+        <v>2.14</v>
       </c>
       <c r="M6" t="n">
-        <v>3.8</v>
+        <v>2.85</v>
       </c>
       <c r="N6" t="n">
-        <v>4.2</v>
+        <v>3.55</v>
       </c>
       <c r="O6" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.63</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="X6" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="Z6" t="n">
         <v>1.5</v>
       </c>
-      <c r="V6" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X6" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2.08</v>
-      </c>
       <c r="AA6" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>['27']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>['60']</t>
+          <t>['1', '65', '76', '78']</t>
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AK6" s="3" t="n">
         <v>45821.5</v>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1303,7 +1303,7 @@
         <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1314,83 +1314,83 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.75</v>
+        <v>1.57</v>
       </c>
       <c r="M7" t="n">
-        <v>3.05</v>
+        <v>3.8</v>
       </c>
       <c r="N7" t="n">
-        <v>2.48</v>
+        <v>4.2</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>4.63</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.3</v>
+        <v>1.72</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.5</v>
+        <v>2.08</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>['66']</t>
+          <t>['27']</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>['58']</t>
+          <t>['60']</t>
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AK7" s="3" t="n">
         <v>45821.5</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,25 +1417,25 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1443,83 +1443,83 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>12</v>
+        <v>2.75</v>
       </c>
       <c r="M8" t="n">
-        <v>5.9</v>
+        <v>3.05</v>
       </c>
       <c r="N8" t="n">
-        <v>1.16</v>
+        <v>2.48</v>
       </c>
       <c r="O8" t="n">
-        <v>8.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.44</v>
+        <v>2.3</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>['9', '68']</t>
+          <t>['66']</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>['19', '36', '50', '71']</t>
+          <t>['58']</t>
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45821.5</v>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,25 +1546,25 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H9" t="n">
         <v>4</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1572,83 +1572,83 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.14</v>
+        <v>12</v>
       </c>
       <c r="M9" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="O9" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="P9" t="n">
         <v>2.85</v>
       </c>
-      <c r="N9" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W9" t="n">
-        <v>1.53</v>
+        <v>1.11</v>
       </c>
       <c r="X9" t="n">
-        <v>2.25</v>
+        <v>5</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.47</v>
+        <v>1.44</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['9', '68']</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>['1', '65', '76', '78']</t>
+          <t>['19', '36', '50', '71']</t>
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45821.5</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,22 +1804,22 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1830,83 +1830,83 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.25</v>
+        <v>2.4</v>
       </c>
       <c r="M11" t="n">
-        <v>3</v>
+        <v>3.45</v>
       </c>
       <c r="N11" t="n">
-        <v>1.88</v>
+        <v>2.42</v>
       </c>
       <c r="O11" t="n">
-        <v>4.1</v>
+        <v>2.94</v>
       </c>
       <c r="P11" t="n">
-        <v>1.77</v>
+        <v>2.26</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.85</v>
+        <v>3.1</v>
       </c>
       <c r="R11" t="n">
-        <v>1.37</v>
+        <v>1.29</v>
       </c>
       <c r="S11" t="n">
-        <v>2.62</v>
+        <v>3.3</v>
       </c>
       <c r="T11" t="n">
-        <v>2.8</v>
+        <v>2.15</v>
       </c>
       <c r="U11" t="n">
-        <v>1.35</v>
+        <v>1.6</v>
       </c>
       <c r="V11" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="W11" t="n">
-        <v>1.33</v>
+        <v>1.13</v>
       </c>
       <c r="X11" t="n">
-        <v>3</v>
+        <v>4.75</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.14</v>
+        <v>1.55</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.69</v>
+        <v>2.3</v>
       </c>
       <c r="AA11" t="n">
-        <v>3.6</v>
+        <v>2.3</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.25</v>
+        <v>1.53</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.85</v>
+        <v>1.5</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.85</v>
+        <v>2.4</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['36', '44']</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['90+4']</t>
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.16</v>
+        <v>1.5</v>
       </c>
       <c r="AI11" t="n">
-        <v>2.75</v>
+        <v>1.8</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.62</v>
+        <v>2.05</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45821.54166666666</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,22 +1933,22 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1959,83 +1959,83 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.4</v>
+        <v>3.25</v>
       </c>
       <c r="M12" t="n">
-        <v>3.45</v>
+        <v>3</v>
       </c>
       <c r="N12" t="n">
-        <v>2.42</v>
+        <v>1.88</v>
       </c>
       <c r="O12" t="n">
-        <v>2.94</v>
+        <v>4.1</v>
       </c>
       <c r="P12" t="n">
-        <v>2.26</v>
+        <v>1.77</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.1</v>
+        <v>2.85</v>
       </c>
       <c r="R12" t="n">
-        <v>1.29</v>
+        <v>1.37</v>
       </c>
       <c r="S12" t="n">
-        <v>3.3</v>
+        <v>2.62</v>
       </c>
       <c r="T12" t="n">
-        <v>2.15</v>
+        <v>2.8</v>
       </c>
       <c r="U12" t="n">
-        <v>1.6</v>
+        <v>1.35</v>
       </c>
       <c r="V12" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="W12" t="n">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="X12" t="n">
-        <v>4.75</v>
+        <v>3</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.55</v>
+        <v>2.14</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.3</v>
+        <v>1.69</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.3</v>
+        <v>3.6</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.53</v>
+        <v>1.25</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.5</v>
+        <v>1.85</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.4</v>
+        <v>1.85</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>['36', '44']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>['90+4']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.5</v>
+        <v>1.16</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.8</v>
+        <v>2.75</v>
       </c>
       <c r="AJ12" t="n">
-        <v>2.05</v>
+        <v>1.62</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45821.54166666666</v>
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>5.96</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2332,7 +2332,7 @@
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -2342,65 +2342,65 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2409,20 +2409,20 @@
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>['63']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AJ15" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AK15" s="3" t="n">
         <v>45821.58333333334</v>
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2707,19 +2707,19 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G18" t="n">
         <v>1</v>
       </c>
       <c r="H18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I18" t="n">
         <v>1</v>
@@ -2733,83 +2733,83 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.75</v>
+        <v>2.88</v>
       </c>
       <c r="M18" t="n">
-        <v>3.18</v>
+        <v>3.03</v>
       </c>
       <c r="N18" t="n">
-        <v>4.2</v>
+        <v>2.26</v>
       </c>
       <c r="O18" t="n">
-        <v>2.15</v>
+        <v>3.8</v>
       </c>
       <c r="P18" t="n">
-        <v>2.1</v>
+        <v>1.87</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.5</v>
+        <v>3.12</v>
       </c>
       <c r="R18" t="n">
-        <v>1.42</v>
+        <v>1.57</v>
       </c>
       <c r="S18" t="n">
-        <v>2.78</v>
+        <v>2.4</v>
       </c>
       <c r="T18" t="n">
-        <v>3.32</v>
+        <v>3.4</v>
       </c>
       <c r="U18" t="n">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="V18" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="W18" t="n">
-        <v>1.33</v>
+        <v>1.48</v>
       </c>
       <c r="X18" t="n">
-        <v>3.1</v>
+        <v>2.66</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.2</v>
+        <v>2.37</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="AA18" t="n">
-        <v>3.7</v>
+        <v>4.4</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.83</v>
+        <v>1.66</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>['18']</t>
+          <t>['32']</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>['10']</t>
+          <t>['12', '83']</t>
         </is>
       </c>
       <c r="AG18" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AH18" t="n">
         <v>1.31</v>
       </c>
-      <c r="AH18" t="n">
-        <v>2.05</v>
-      </c>
       <c r="AI18" t="n">
-        <v>1.53</v>
+        <v>2.4</v>
       </c>
       <c r="AJ18" t="n">
-        <v>3.1</v>
+        <v>1.8</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45821.65625</v>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,25 +2836,25 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
         <v>2</v>
       </c>
-      <c r="H19" t="n">
-        <v>1</v>
-      </c>
       <c r="I19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -2862,83 +2862,83 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.22</v>
+        <v>3.94</v>
       </c>
       <c r="M19" t="n">
-        <v>3.36</v>
+        <v>3.27</v>
       </c>
       <c r="N19" t="n">
-        <v>2.69</v>
+        <v>1.79</v>
       </c>
       <c r="O19" t="n">
-        <v>2.9</v>
+        <v>4.1</v>
       </c>
       <c r="P19" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="Q19" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X19" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AA19" t="n">
         <v>3.2</v>
       </c>
-      <c r="R19" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S19" t="n">
-        <v>3</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X19" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>2.8</v>
-      </c>
       <c r="AB19" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.55</v>
+        <v>1.8</v>
       </c>
       <c r="AD19" t="n">
-        <v>2.23</v>
+        <v>1.91</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>['10', '59']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>['90']</t>
+          <t>['11', '44']</t>
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.56</v>
+        <v>1.24</v>
       </c>
       <c r="AI19" t="n">
-        <v>1.8</v>
+        <v>2.88</v>
       </c>
       <c r="AJ19" t="n">
-        <v>2.03</v>
+        <v>1.53</v>
       </c>
       <c r="AK19" s="3" t="n">
         <v>45821.65625</v>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,25 +2965,25 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -2991,83 +2991,83 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.66</v>
+        <v>1.67</v>
       </c>
       <c r="M20" t="n">
-        <v>3.32</v>
+        <v>3.41</v>
       </c>
       <c r="N20" t="n">
-        <v>2.26</v>
+        <v>4.4</v>
       </c>
       <c r="O20" t="n">
-        <v>3.85</v>
+        <v>2.3</v>
       </c>
       <c r="P20" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.55</v>
+        <v>4</v>
       </c>
       <c r="R20" t="n">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="S20" t="n">
-        <v>2.95</v>
+        <v>2.81</v>
       </c>
       <c r="T20" t="n">
-        <v>2.55</v>
+        <v>2.85</v>
       </c>
       <c r="U20" t="n">
-        <v>1.45</v>
+        <v>1.37</v>
       </c>
       <c r="V20" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="W20" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="X20" t="n">
-        <v>3.75</v>
+        <v>3.1</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.77</v>
+        <v>1.95</v>
       </c>
       <c r="Z20" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AD20" t="n">
         <v>1.93</v>
       </c>
-      <c r="AA20" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>['72']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>['5']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.3</v>
+        <v>2.13</v>
       </c>
       <c r="AI20" t="n">
-        <v>2.07</v>
+        <v>1.5</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.81</v>
+        <v>3</v>
       </c>
       <c r="AK20" s="3" t="n">
         <v>45821.65625</v>
@@ -3094,25 +3094,25 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -3120,83 +3120,83 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.94</v>
+        <v>1.75</v>
       </c>
       <c r="M21" t="n">
-        <v>3.27</v>
+        <v>3.18</v>
       </c>
       <c r="N21" t="n">
-        <v>1.79</v>
+        <v>4.2</v>
       </c>
       <c r="O21" t="n">
-        <v>4.1</v>
+        <v>2.15</v>
       </c>
       <c r="P21" t="n">
         <v>2.1</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.4</v>
+        <v>4.5</v>
       </c>
       <c r="R21" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="S21" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="T21" t="n">
-        <v>2.98</v>
+        <v>3.32</v>
       </c>
       <c r="U21" t="n">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="V21" t="n">
         <v>1.06</v>
       </c>
       <c r="W21" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="X21" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.94</v>
+        <v>2.2</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.76</v>
+        <v>1.53</v>
       </c>
       <c r="AA21" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.8</v>
+        <v>1.98</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['18']</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>['11', '44']</t>
+          <t>['10']</t>
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.24</v>
+        <v>2.05</v>
       </c>
       <c r="AI21" t="n">
-        <v>2.88</v>
+        <v>1.53</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.53</v>
+        <v>3.1</v>
       </c>
       <c r="AK21" s="3" t="n">
         <v>45821.65625</v>
@@ -3223,25 +3223,25 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -3249,43 +3249,43 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.34</v>
+        <v>1.46</v>
       </c>
       <c r="M22" t="n">
-        <v>3.23</v>
+        <v>3.8</v>
       </c>
       <c r="N22" t="n">
-        <v>2.62</v>
+        <v>5.9</v>
       </c>
       <c r="O22" t="n">
-        <v>3.4</v>
+        <v>2.05</v>
       </c>
       <c r="P22" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="Q22" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S22" t="n">
         <v>2.95</v>
       </c>
-      <c r="R22" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2.8</v>
-      </c>
       <c r="T22" t="n">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="U22" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="V22" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="W22" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="X22" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="Y22" t="n">
         <v>1.92</v>
@@ -3294,38 +3294,38 @@
         <v>1.78</v>
       </c>
       <c r="AA22" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.96</v>
+        <v>1.68</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>['49', '89']</t>
+          <t>['27']</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>['51', '67']</t>
+          <t>['35']</t>
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.55</v>
+        <v>1.2</v>
       </c>
       <c r="AH22" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AI22" t="n">
         <v>1.4</v>
       </c>
-      <c r="AI22" t="n">
-        <v>1.88</v>
-      </c>
       <c r="AJ22" t="n">
-        <v>2.02</v>
+        <v>3.42</v>
       </c>
       <c r="AK22" s="3" t="n">
         <v>45821.65625</v>
@@ -3352,25 +3352,25 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -3378,43 +3378,43 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.46</v>
+        <v>2.34</v>
       </c>
       <c r="M23" t="n">
-        <v>3.8</v>
+        <v>3.23</v>
       </c>
       <c r="N23" t="n">
-        <v>5.9</v>
+        <v>2.62</v>
       </c>
       <c r="O23" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P23" t="n">
         <v>2.05</v>
       </c>
-      <c r="P23" t="n">
-        <v>2.25</v>
-      </c>
       <c r="Q23" t="n">
-        <v>5.25</v>
+        <v>2.95</v>
       </c>
       <c r="R23" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="S23" t="n">
-        <v>2.95</v>
+        <v>2.8</v>
       </c>
       <c r="T23" t="n">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="U23" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="V23" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="W23" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="X23" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="Y23" t="n">
         <v>1.92</v>
@@ -3423,38 +3423,38 @@
         <v>1.78</v>
       </c>
       <c r="AA23" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.68</v>
+        <v>1.96</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>['27']</t>
+          <t>['49', '89']</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>['35']</t>
+          <t>['51', '67']</t>
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.2</v>
+        <v>1.55</v>
       </c>
       <c r="AH23" t="n">
-        <v>2.35</v>
+        <v>1.4</v>
       </c>
       <c r="AI23" t="n">
-        <v>1.4</v>
+        <v>1.88</v>
       </c>
       <c r="AJ23" t="n">
-        <v>3.42</v>
+        <v>2.02</v>
       </c>
       <c r="AK23" s="3" t="n">
         <v>45821.65625</v>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,25 +3481,25 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -3507,83 +3507,83 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.67</v>
+        <v>2.66</v>
       </c>
       <c r="M24" t="n">
-        <v>3.41</v>
+        <v>3.32</v>
       </c>
       <c r="N24" t="n">
-        <v>4.4</v>
+        <v>2.26</v>
       </c>
       <c r="O24" t="n">
-        <v>2.3</v>
+        <v>3.85</v>
       </c>
       <c r="P24" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="Q24" t="n">
-        <v>4</v>
+        <v>2.55</v>
       </c>
       <c r="R24" t="n">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="S24" t="n">
-        <v>2.81</v>
+        <v>2.95</v>
       </c>
       <c r="T24" t="n">
-        <v>2.85</v>
+        <v>2.55</v>
       </c>
       <c r="U24" t="n">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="V24" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="W24" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X24" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>['72']</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>['5']</t>
+        </is>
+      </c>
+      <c r="AG24" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AH24" t="n">
         <v>1.3</v>
       </c>
-      <c r="X24" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AE24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG24" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>2.13</v>
-      </c>
       <c r="AI24" t="n">
-        <v>1.5</v>
+        <v>2.07</v>
       </c>
       <c r="AJ24" t="n">
-        <v>3</v>
+        <v>1.81</v>
       </c>
       <c r="AK24" s="3" t="n">
         <v>45821.65625</v>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,25 +3610,25 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G25" t="n">
+        <v>2</v>
+      </c>
+      <c r="H25" t="n">
         <v>1</v>
-      </c>
-      <c r="H25" t="n">
-        <v>2</v>
       </c>
       <c r="I25" t="n">
         <v>1</v>
       </c>
       <c r="J25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -3636,83 +3636,83 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.88</v>
+        <v>2.22</v>
       </c>
       <c r="M25" t="n">
-        <v>3.03</v>
+        <v>3.36</v>
       </c>
       <c r="N25" t="n">
-        <v>2.26</v>
+        <v>2.69</v>
       </c>
       <c r="O25" t="n">
-        <v>3.8</v>
+        <v>2.9</v>
       </c>
       <c r="P25" t="n">
-        <v>1.87</v>
+        <v>2.15</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.12</v>
+        <v>3.2</v>
       </c>
       <c r="R25" t="n">
-        <v>1.57</v>
+        <v>1.33</v>
       </c>
       <c r="S25" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="T25" t="n">
-        <v>3.4</v>
+        <v>2.65</v>
       </c>
       <c r="U25" t="n">
-        <v>1.27</v>
+        <v>1.48</v>
       </c>
       <c r="V25" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="W25" t="n">
-        <v>1.48</v>
+        <v>1.22</v>
       </c>
       <c r="X25" t="n">
-        <v>2.66</v>
+        <v>3.85</v>
       </c>
       <c r="Y25" t="n">
-        <v>2.37</v>
+        <v>1.7</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.48</v>
+        <v>1.95</v>
       </c>
       <c r="AA25" t="n">
-        <v>4.4</v>
+        <v>2.8</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.18</v>
+        <v>1.4</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.05</v>
+        <v>1.55</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.66</v>
+        <v>2.23</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>['32']</t>
+          <t>['10', '59']</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>['12', '83']</t>
+          <t>['90']</t>
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.31</v>
+        <v>1.56</v>
       </c>
       <c r="AI25" t="n">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1.8</v>
+        <v>2.03</v>
       </c>
       <c r="AK25" s="3" t="n">
         <v>45821.65625</v>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,25 +3868,25 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -3894,83 +3894,83 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.12</v>
+        <v>3.46</v>
       </c>
       <c r="M27" t="n">
-        <v>3.43</v>
+        <v>3.4</v>
       </c>
       <c r="N27" t="n">
-        <v>3.36</v>
+        <v>1.94</v>
       </c>
       <c r="O27" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="P27" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S27" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X27" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>['61', '68']</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>['17', '36', '51']</t>
+        </is>
+      </c>
+      <c r="AG27" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI27" t="n">
         <v>2.88</v>
       </c>
-      <c r="P27" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>4</v>
-      </c>
-      <c r="R27" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S27" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T27" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V27" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="X27" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AE27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF27" t="inlineStr">
-        <is>
-          <t>['63']</t>
-        </is>
-      </c>
-      <c r="AG27" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>1.67</v>
-      </c>
       <c r="AJ27" t="n">
-        <v>2.5</v>
+        <v>1.57</v>
       </c>
       <c r="AK27" s="3" t="n">
         <v>45821.875</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,25 +3997,25 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -4023,83 +4023,83 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>3.46</v>
+        <v>2.12</v>
       </c>
       <c r="M28" t="n">
-        <v>3.4</v>
+        <v>3.43</v>
       </c>
       <c r="N28" t="n">
-        <v>1.94</v>
+        <v>3.36</v>
       </c>
       <c r="O28" t="n">
-        <v>3.85</v>
+        <v>2.88</v>
       </c>
       <c r="P28" t="n">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="Q28" t="n">
+        <v>4</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S28" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T28" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="X28" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>['63']</t>
+        </is>
+      </c>
+      <c r="AG28" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AJ28" t="n">
         <v>2.5</v>
-      </c>
-      <c r="R28" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="S28" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="T28" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="V28" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X28" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AE28" t="inlineStr">
-        <is>
-          <t>['61', '68']</t>
-        </is>
-      </c>
-      <c r="AF28" t="inlineStr">
-        <is>
-          <t>['17', '36', '51']</t>
-        </is>
-      </c>
-      <c r="AG28" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>1.57</v>
       </c>
       <c r="AK28" s="3" t="n">
         <v>45821.875</v>
